--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008566648607316726</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>51789089</v>
+        <v>3900427</v>
       </c>
       <c r="L2" t="n">
-        <v>26898220</v>
+        <v>1637872</v>
       </c>
       <c r="M2" t="n">
-        <v>5940070</v>
+        <v>282667</v>
       </c>
       <c r="N2" t="n">
-        <v>251310</v>
+        <v>5991</v>
       </c>
       <c r="O2" t="n">
-        <v>3451342</v>
+        <v>141835</v>
       </c>
       <c r="P2" t="n">
-        <v>1298380</v>
+        <v>41854</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999894917011261</v>
+        <v>0.9998088479042053</v>
       </c>
       <c r="R2" t="n">
-        <v>0.820531964302063</v>
+        <v>0.7048280835151672</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6855442523956299</v>
+        <v>0.5155386328697205</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6166325807571411</v>
+        <v>0.379994124174118</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1813105344772339</v>
+        <v>0.04055206477642059</v>
       </c>
       <c r="V2" t="n">
-        <v>0.666925847530365</v>
+        <v>0.4190722405910492</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7894946336746216</v>
+        <v>0.5619797110557556</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002053537536211935</v>
       </c>
       <c r="C3" t="n">
-        <v>984</v>
+        <v>225</v>
       </c>
       <c r="D3" t="n">
-        <v>51789089</v>
+        <v>3900427</v>
       </c>
       <c r="E3" t="n">
-        <v>7890869</v>
+        <v>972775</v>
       </c>
       <c r="F3" t="n">
-        <v>228165</v>
+        <v>46032</v>
       </c>
       <c r="G3" t="n">
-        <v>22393</v>
+        <v>4667</v>
       </c>
       <c r="H3" t="n">
-        <v>15143</v>
+        <v>3951</v>
       </c>
       <c r="I3" t="n">
-        <v>1563</v>
+        <v>433</v>
       </c>
       <c r="J3" t="n">
-        <v>120191503</v>
+        <v>10015415</v>
       </c>
       <c r="K3" t="n">
-        <v>124679605</v>
+        <v>9767647</v>
       </c>
       <c r="L3" t="n">
-        <v>144129817</v>
+        <v>11444993</v>
       </c>
       <c r="M3" t="n">
-        <v>181020352</v>
+        <v>14922864</v>
       </c>
       <c r="N3" t="n">
-        <v>193746842</v>
+        <v>16097786</v>
       </c>
       <c r="O3" t="n">
-        <v>188105614</v>
+        <v>15619991</v>
       </c>
       <c r="P3" t="n">
-        <v>193286414</v>
+        <v>16102928</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8638972043991089</v>
+        <v>0.7914008498191833</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6811865568161011</v>
+        <v>0.4895793497562408</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5283894538879395</v>
+        <v>0.2989505231380463</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2340831160545349</v>
+        <v>0.06651566922664642</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5633991360664368</v>
+        <v>0.2764847278594971</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5590212941169739</v>
+        <v>0.2156866788864136</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03228002292548469</v>
       </c>
       <c r="C4" t="n">
-        <v>363</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>10367443</v>
+        <v>1443783</v>
       </c>
       <c r="E4" t="n">
-        <v>26898220</v>
+        <v>1637872</v>
       </c>
       <c r="F4" t="n">
-        <v>1848362</v>
+        <v>205484</v>
       </c>
       <c r="G4" t="n">
-        <v>145010</v>
+        <v>23092</v>
       </c>
       <c r="H4" t="n">
-        <v>204722</v>
+        <v>31345</v>
       </c>
       <c r="I4" t="n">
-        <v>23183</v>
+        <v>3859</v>
       </c>
       <c r="J4" t="n">
-        <v>7961</v>
+        <v>1207</v>
       </c>
       <c r="K4" t="n">
-        <v>11327389</v>
+        <v>1633443</v>
       </c>
       <c r="L4" t="n">
-        <v>12338080</v>
+        <v>1539139</v>
       </c>
       <c r="M4" t="n">
-        <v>3693008</v>
+        <v>461205</v>
       </c>
       <c r="N4" t="n">
-        <v>1134765</v>
+        <v>141745</v>
       </c>
       <c r="O4" t="n">
-        <v>1723659</v>
+        <v>196615</v>
       </c>
       <c r="P4" t="n">
-        <v>346191</v>
+        <v>32622</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999474883079529</v>
+        <v>0.999904453754425</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8416563868522644</v>
+        <v>0.7456098794937134</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6833584308624268</v>
+        <v>0.5022237300872803</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5691106915473938</v>
+        <v>0.3346353471279144</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2043446451425552</v>
+        <v>0.05038581788539886</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6108068227767944</v>
+        <v>0.3331634104251862</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6545629501342773</v>
+        <v>0.3117314577102661</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1367</v>
+        <v>281</v>
       </c>
       <c r="D5" t="n">
-        <v>690935</v>
+        <v>139495</v>
       </c>
       <c r="E5" t="n">
-        <v>3521566</v>
+        <v>409231</v>
       </c>
       <c r="F5" t="n">
-        <v>5940070</v>
+        <v>282667</v>
       </c>
       <c r="G5" t="n">
-        <v>335752</v>
+        <v>37290</v>
       </c>
       <c r="H5" t="n">
-        <v>672061</v>
+        <v>65878</v>
       </c>
       <c r="I5" t="n">
-        <v>80089</v>
+        <v>10689</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8159117</v>
+        <v>1028083</v>
       </c>
       <c r="L5" t="n">
-        <v>12589083</v>
+        <v>1707596</v>
       </c>
       <c r="M5" t="n">
-        <v>5301770</v>
+        <v>662864</v>
       </c>
       <c r="N5" t="n">
-        <v>822283</v>
+        <v>84078</v>
       </c>
       <c r="O5" t="n">
-        <v>2674585</v>
+        <v>371159</v>
       </c>
       <c r="P5" t="n">
-        <v>1024215</v>
+        <v>152196</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999593496322632</v>
+        <v>0.9999260902404785</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9005563259124756</v>
+        <v>0.8370121717453003</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8727915287017822</v>
+        <v>0.8011748790740967</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9540978074073792</v>
+        <v>0.9311637282371521</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9900127649307251</v>
+        <v>0.9861709475517273</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9775548577308655</v>
+        <v>0.965230405330658</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9930065274238586</v>
+        <v>0.9886820316314697</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>222</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>183302</v>
+        <v>23947</v>
       </c>
       <c r="E6" t="n">
-        <v>279641</v>
+        <v>28817</v>
       </c>
       <c r="F6" t="n">
-        <v>253910</v>
+        <v>23375</v>
       </c>
       <c r="G6" t="n">
-        <v>251310</v>
+        <v>5991</v>
       </c>
       <c r="H6" t="n">
-        <v>95066</v>
+        <v>7005</v>
       </c>
       <c r="I6" t="n">
-        <v>10142</v>
+        <v>898</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1787</v>
+        <v>235</v>
       </c>
       <c r="D7" t="n">
-        <v>78796</v>
+        <v>23594</v>
       </c>
       <c r="E7" t="n">
-        <v>585487</v>
+        <v>113744</v>
       </c>
       <c r="F7" t="n">
-        <v>1231783</v>
+        <v>156948</v>
       </c>
       <c r="G7" t="n">
-        <v>545518</v>
+        <v>59895</v>
       </c>
       <c r="H7" t="n">
-        <v>3451342</v>
+        <v>141835</v>
       </c>
       <c r="I7" t="n">
-        <v>231214</v>
+        <v>16743</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3238</v>
+        <v>397</v>
       </c>
       <c r="D8" t="n">
-        <v>6913</v>
+        <v>2624</v>
       </c>
       <c r="E8" t="n">
-        <v>60517</v>
+        <v>14572</v>
       </c>
       <c r="F8" t="n">
-        <v>130788</v>
+        <v>29366</v>
       </c>
       <c r="G8" t="n">
-        <v>86092</v>
+        <v>16801</v>
       </c>
       <c r="H8" t="n">
-        <v>736667</v>
+        <v>88436</v>
       </c>
       <c r="I8" t="n">
-        <v>1298380</v>
+        <v>41854</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
